--- a/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
+++ b/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
@@ -892,7 +892,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2001</t>
         </is>
       </c>
       <c r="G3" s="45" t="n"/>

--- a/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
+++ b/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
@@ -892,7 +892,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2001</t>
+15/15/2015</t>
         </is>
       </c>
       <c r="G3" s="45" t="n"/>

--- a/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
+++ b/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
@@ -892,7 +892,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-15/15/2015</t>
+22/02/2025</t>
         </is>
       </c>
       <c r="G3" s="45" t="n"/>

--- a/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
+++ b/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
@@ -892,7 +892,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2000</t>
         </is>
       </c>
       <c r="G3" s="45" t="n"/>

--- a/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
+++ b/Syllabus_Electronica/Ingeniería en Control y Automatización/Área Profesional/Electivas/7338 - Bases de datos en ingeniería.xlsx
@@ -892,7 +892,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2000</t>
+10/10/2000</t>
         </is>
       </c>
       <c r="G3" s="45" t="n"/>
